--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -827,9 +827,6 @@
     <t>診断レポートの分野を表すコード。【詳細参照】</t>
   </si>
   <si>
-    <t>診断レポートを作成した臨床分野、部門、または診断サービス（心臓病学、生化学、血液学、放射線医学など）を分類するコード</t>
-  </si>
-  <si>
     <t>JP_DiagnosticReportCategory_VSの中から「LP7796-8」（Endoscopy（内視鏡））を指定する。</t>
   </si>
   <si>
@@ -1133,11 +1130,14 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_Endoscopy)
 </t>
   </si>
   <si>
-    <t>この診断レポートの一部となるObservationに関する情報。</t>
+    <t>この診断レポートの一部となる内視鏡検査、治療による観察結果（診断、所見など）の情報。【詳細参照】</t>
+  </si>
+  <si>
+    <t>この診断レポートの一部となる内視鏡検査、治療による観察結果（診断、所見など）の情報。詳細はJP_Observation_Endoscopyの実装ガイドを参照</t>
   </si>
   <si>
     <t>Observationsは階層構造を持てる。</t>
@@ -1239,7 +1239,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Media_Endoscopy)
 </t>
   </si>
   <si>
@@ -2957,7 +2957,7 @@
         <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>81</v>
@@ -4576,10 +4576,10 @@
         <v>259</v>
       </c>
       <c r="M26" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4609,7 +4609,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4656,7 +4656,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>192</v>
@@ -4768,7 +4768,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>198</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>203</v>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>212</v>
@@ -5110,7 +5110,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>213</v>
@@ -5224,7 +5224,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>214</v>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -5340,7 +5340,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>221</v>
@@ -5454,7 +5454,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>228</v>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>81</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>234</v>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>240</v>
@@ -5798,7 +5798,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>249</v>
@@ -5914,14 +5914,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5943,13 +5943,13 @@
         <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5975,11 +5975,11 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5997,7 +5997,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>90</v>
@@ -6012,28 +6012,28 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>286</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6052,19 +6052,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6113,7 +6113,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6128,28 +6128,28 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6168,19 +6168,19 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6229,7 +6229,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6244,28 +6244,28 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>308</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6284,19 +6284,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6345,7 +6345,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6360,28 +6360,28 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>319</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6400,19 +6400,19 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6461,7 +6461,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6479,25 +6479,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6516,19 +6516,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6577,7 +6577,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6592,28 +6592,28 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6632,19 +6632,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>346</v>
-      </c>
       <c r="O44" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6693,7 +6693,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6708,24 +6708,24 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>340</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6748,19 +6748,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6809,7 +6809,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6827,10 +6827,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6838,14 +6838,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6855,7 +6855,7 @@
         <v>80</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>81</v>
@@ -6864,10 +6864,10 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>358</v>
@@ -6925,7 +6925,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7561,7 +7561,7 @@
         <v>386</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O52" t="s" s="2">
         <v>387</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -818,10 +818,10 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:endoscopy</t>
-  </si>
-  <si>
-    <t>endoscopy</t>
+    <t>DiagnosticReport.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
   </si>
   <si>
     <t>診断レポートの分野を表すコード。【詳細参照】</t>
@@ -833,43 +833,43 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:endoscopy.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding.system</t>
+    <t>DiagnosticReport.category:first.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.system</t>
   </si>
   <si>
     <t>http://loinc.org</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:endoscopy.coding.version</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding.code</t>
+    <t>DiagnosticReport.category:first.coding.version</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.code</t>
   </si>
   <si>
     <t>LP7796-8</t>
   </si>
   <si>
-    <t>DiagnosticReport.category:endoscopy.coding.display</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.coding.userSelected</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.category:endoscopy.text</t>
+    <t>DiagnosticReport.category:first.coding.display</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.coding.userSelected</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:first.text</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -1633,7 +1633,7 @@
   <dimension ref="A1:AN56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.33984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.01171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.8125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -277,7 +277,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -321,16 +321,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -456,7 +456,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -277,7 +277,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -1633,17 +1633,17 @@
   <dimension ref="A1:AN56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.01171875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.8125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="62.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.01953125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.41796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="53.34375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="207.65625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="178.02734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1652,26 +1652,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="55.07421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.30078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.21484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.26953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="171.66796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="121.93359375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="147.17578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="104.53515625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -4561,7 +4561,7 @@
         <v>90</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -375,7 +375,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -600,7 +600,7 @@
     <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -1104,7 +1104,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -2938,7 +2938,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>157</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>257</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>286</v>
       </c>
@@ -6256,7 +6256,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>308</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>319</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>329</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>340</v>
       </c>
@@ -6836,7 +6836,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>354</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>363</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>389</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>393</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>401</v>
       </c>
@@ -7980,7 +7980,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>407</v>
       </c>
@@ -8098,12 +8098,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN56">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="413">
   <si>
     <t>Property</t>
   </si>
@@ -603,7 +603,7 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -849,9 +849,6 @@
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.version</t>
@@ -5269,7 +5266,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>268</v>
+        <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -5340,7 +5337,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>221</v>
@@ -5454,7 +5451,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>228</v>
@@ -5497,10 +5494,10 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>271</v>
+        <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>81</v>
+        <v>270</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -5568,7 +5565,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>234</v>
@@ -5682,7 +5679,7 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>240</v>
@@ -5798,7 +5795,7 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>249</v>
@@ -5914,14 +5911,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5943,13 +5940,13 @@
         <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5975,11 +5972,11 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5997,7 +5994,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>90</v>
@@ -6012,28 +6009,28 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6052,19 +6049,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6113,7 +6110,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6128,28 +6125,28 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>296</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6168,19 +6165,19 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>303</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6229,7 +6226,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6244,28 +6241,28 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6284,19 +6281,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6345,7 +6342,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6360,28 +6357,28 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>318</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6400,19 +6397,19 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6461,7 +6458,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6479,25 +6476,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>328</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6516,19 +6513,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6577,7 +6574,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6592,28 +6589,28 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6632,19 +6629,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="N44" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="O44" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6693,7 +6690,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6708,24 +6705,24 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6748,19 +6745,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>352</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6809,7 +6806,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6827,10 +6824,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6838,14 +6835,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6864,19 +6861,19 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -6925,7 +6922,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6943,10 +6940,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6954,10 +6951,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6980,16 +6977,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7039,7 +7036,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7060,7 +7057,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7068,14 +7065,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7094,19 +7091,19 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7155,7 +7152,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7173,10 +7170,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7184,10 +7181,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7296,10 +7293,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7410,14 +7407,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7439,10 +7436,10 @@
         <v>136</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>139</v>
@@ -7497,7 +7494,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7526,10 +7523,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7555,16 +7552,16 @@
         <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="O52" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7613,7 +7610,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7634,7 +7631,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7642,10 +7639,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7668,13 +7665,13 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="M53" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7725,7 +7722,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>90</v>
@@ -7746,7 +7743,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7754,14 +7751,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7783,16 +7780,16 @@
         <v>193</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7841,7 +7838,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7859,10 +7856,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -7870,10 +7867,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7899,13 +7896,13 @@
         <v>181</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7935,7 +7932,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -7953,7 +7950,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7971,10 +7968,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7982,10 +7979,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8008,19 +8005,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8069,7 +8066,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8087,10 +8084,10 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -272,7 +272,7 @@
     <t>内視鏡を使用して実施された検査、治療に関する診断レポート。</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
 【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
   </si>
   <si>
@@ -491,7 +491,7 @@
     <t>製品またはシステムが管理する、施設内で診断レポートを一意に識別するためのID。</t>
   </si>
   <si>
-    <t>通常、診断サービスプロバイダの情報システム（フィラーID）によって割り当てられる。</t>
+    <t>通常、診断サービスを実施した施設の情報システム（実施者ID、HL7 v2 の filler ID）によって割り当てられる。</t>
   </si>
   <si>
     <t>発生源の検査室からこのレポートについてクエリを作成するとき、およびFHIRコンテキスト外のレポートにリンクするときに使用する識別子を知る必要がある。</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -830,6 +830,15 @@
     <t>JP_DiagnosticReportCategory_VSの中から「LP7796-8」（Endoscopy（内視鏡））を指定する。</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://loinc.org"/&gt;
+    &lt;code value="LP7796-8"/&gt;
+    &lt;display value="Endoscopy（内視鏡）"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
@@ -855,9 +864,6 @@
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.code</t>
-  </si>
-  <si>
-    <t>LP7796-8</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.display</t>
@@ -4587,7 +4593,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>81</v>
+        <v>261</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -4606,7 +4612,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4653,7 +4659,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>192</v>
@@ -4765,7 +4771,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>198</v>
@@ -4879,7 +4885,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>203</v>
@@ -4995,7 +5001,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>212</v>
@@ -5107,7 +5113,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>213</v>
@@ -5221,7 +5227,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>214</v>
@@ -5337,7 +5343,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>221</v>
@@ -5451,7 +5457,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>228</v>
@@ -5497,7 +5503,7 @@
         <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-diagnosticreport-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2073" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="411">
   <si>
     <t>Property</t>
   </si>
@@ -594,13 +594,7 @@
     <t>これは、検索、並べ替え、および表示の目的で使用される。</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>診断サービスセクションのコード。 / Codes for diagnostic service sections.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:$this}
@@ -839,9 +833,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DiagnosticReportCategory_VS</t>
-  </si>
-  <si>
     <t>DiagnosticReport.category:first.id</t>
   </si>
   <si>
@@ -1287,6 +1278,9 @@
   </si>
   <si>
     <t>JED Project（https://jedproject.jges.net/）が対象とする検査種別については、指定された質的診断コードを使用することを強く推奨する。</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ConclusionCodesJed_VS</t>
@@ -1660,7 +1654,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="47.21484375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="42.453125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="54.26953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -3236,26 +3230,24 @@
         <v>81</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Y14" s="2"/>
+      <c r="Z14" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Y14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB14" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>179</v>
@@ -3276,21 +3268,21 @@
         <v>81</v>
       </c>
       <c r="AL14" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AM14" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>191</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3313,13 +3305,13 @@
         <v>81</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3370,7 +3362,7 @@
         <v>81</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -3391,7 +3383,7 @@
         <v>81</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>81</v>
@@ -3399,10 +3391,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3431,7 +3423,7 @@
         <v>137</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>139</v>
@@ -3472,19 +3464,19 @@
         <v>81</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3505,7 +3497,7 @@
         <v>81</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>81</v>
@@ -3513,10 +3505,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3539,19 +3531,19 @@
         <v>91</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>81</v>
@@ -3600,7 +3592,7 @@
         <v>81</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3618,10 +3610,10 @@
         <v>81</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>81</v>
@@ -3629,10 +3621,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3655,13 +3647,13 @@
         <v>81</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3712,7 +3704,7 @@
         <v>81</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3733,7 +3725,7 @@
         <v>81</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>81</v>
@@ -3741,10 +3733,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3773,7 +3765,7 @@
         <v>137</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N19" t="s" s="2">
         <v>139</v>
@@ -3814,19 +3806,19 @@
         <v>81</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AF19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3847,7 +3839,7 @@
         <v>81</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>81</v>
@@ -3855,10 +3847,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3884,16 +3876,16 @@
         <v>104</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>81</v>
@@ -3942,7 +3934,7 @@
         <v>81</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3960,10 +3952,10 @@
         <v>81</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>81</v>
@@ -3971,10 +3963,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3997,16 +3989,16 @@
         <v>91</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4056,7 +4048,7 @@
         <v>81</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4074,10 +4066,10 @@
         <v>81</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>81</v>
@@ -4085,10 +4077,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4114,14 +4106,14 @@
         <v>110</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>81</v>
@@ -4170,7 +4162,7 @@
         <v>81</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -4188,10 +4180,10 @@
         <v>81</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>81</v>
@@ -4199,10 +4191,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4225,17 +4217,17 @@
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>81</v>
@@ -4284,7 +4276,7 @@
         <v>81</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4302,10 +4294,10 @@
         <v>81</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>81</v>
@@ -4313,10 +4305,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4339,19 +4331,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>81</v>
@@ -4400,7 +4392,7 @@
         <v>81</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -4418,10 +4410,10 @@
         <v>81</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>81</v>
@@ -4429,10 +4421,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4455,19 +4447,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>81</v>
@@ -4516,7 +4508,7 @@
         <v>81</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -4534,10 +4526,10 @@
         <v>81</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>81</v>
@@ -4545,13 +4537,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>179</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>180</v>
@@ -4576,13 +4568,13 @@
         <v>181</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>182</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4593,7 +4585,7 @@
         <v>81</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>81</v>
@@ -4612,7 +4604,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>262</v>
+        <v>184</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>81</v>
@@ -4648,21 +4640,21 @@
         <v>81</v>
       </c>
       <c r="AL26" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>191</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4685,13 +4677,13 @@
         <v>81</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4742,7 +4734,7 @@
         <v>81</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -4763,7 +4755,7 @@
         <v>81</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>81</v>
@@ -4771,10 +4763,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4803,7 +4795,7 @@
         <v>137</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>139</v>
@@ -4844,19 +4836,19 @@
         <v>81</v>
       </c>
       <c r="AB28" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4877,7 +4869,7 @@
         <v>81</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>81</v>
@@ -4885,10 +4877,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4911,19 +4903,19 @@
         <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>81</v>
@@ -4972,7 +4964,7 @@
         <v>81</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -4990,10 +4982,10 @@
         <v>81</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>81</v>
@@ -5001,10 +4993,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5027,13 +5019,13 @@
         <v>81</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5084,7 +5076,7 @@
         <v>81</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5105,7 +5097,7 @@
         <v>81</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>81</v>
@@ -5113,10 +5105,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5145,7 +5137,7 @@
         <v>137</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>139</v>
@@ -5186,19 +5178,19 @@
         <v>81</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -5219,7 +5211,7 @@
         <v>81</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>81</v>
@@ -5227,10 +5219,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5256,16 +5248,16 @@
         <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>81</v>
@@ -5314,7 +5306,7 @@
         <v>81</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5332,10 +5324,10 @@
         <v>81</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>81</v>
@@ -5343,10 +5335,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5369,16 +5361,16 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5428,7 +5420,7 @@
         <v>81</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5446,10 +5438,10 @@
         <v>81</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>81</v>
@@ -5457,10 +5449,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5486,14 +5478,14 @@
         <v>110</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>81</v>
@@ -5542,7 +5534,7 @@
         <v>81</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5560,10 +5552,10 @@
         <v>81</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>81</v>
@@ -5571,10 +5563,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5597,17 +5589,17 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>81</v>
@@ -5656,7 +5648,7 @@
         <v>81</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5674,10 +5666,10 @@
         <v>81</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>81</v>
@@ -5685,10 +5677,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5711,19 +5703,19 @@
         <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>245</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>81</v>
@@ -5772,7 +5764,7 @@
         <v>81</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5790,10 +5782,10 @@
         <v>81</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>81</v>
@@ -5801,10 +5793,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5827,19 +5819,19 @@
         <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>253</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>81</v>
@@ -5888,7 +5880,7 @@
         <v>81</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5906,10 +5898,10 @@
         <v>81</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>81</v>
@@ -5917,14 +5909,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5946,13 +5938,13 @@
         <v>181</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5978,11 +5970,11 @@
         <v>81</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -6000,7 +5992,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>90</v>
@@ -6015,28 +6007,28 @@
         <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6055,19 +6047,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6116,7 +6108,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6131,28 +6123,28 @@
         <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>295</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6171,19 +6163,19 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6232,7 +6224,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6247,28 +6239,28 @@
         <v>102</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>306</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6287,19 +6279,19 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6348,7 +6340,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6363,28 +6355,28 @@
         <v>102</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>317</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6403,19 +6395,19 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6464,7 +6456,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6482,25 +6474,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6519,19 +6511,19 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6580,7 +6572,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6595,28 +6587,28 @@
         <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>338</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6635,19 +6627,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="L44" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>344</v>
-      </c>
       <c r="O44" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6696,7 +6688,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6711,24 +6703,24 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>338</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6751,19 +6743,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6812,7 +6804,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6830,10 +6822,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6841,14 +6833,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6867,19 +6859,19 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -6928,7 +6920,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6946,10 +6938,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6957,10 +6949,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6983,16 +6975,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7042,7 +7034,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7063,7 +7055,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7071,14 +7063,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7097,19 +7089,19 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7158,7 +7150,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7176,10 +7168,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7187,10 +7179,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7213,13 +7205,13 @@
         <v>81</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="L49" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7270,7 +7262,7 @@
         <v>81</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7291,7 +7283,7 @@
         <v>81</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>81</v>
@@ -7299,10 +7291,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7331,7 +7323,7 @@
         <v>137</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>139</v>
@@ -7384,7 +7376,7 @@
         <v>81</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7405,7 +7397,7 @@
         <v>81</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>81</v>
@@ -7413,14 +7405,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7442,10 +7434,10 @@
         <v>136</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>139</v>
@@ -7500,7 +7492,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7529,10 +7521,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7555,19 +7547,19 @@
         <v>81</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7616,7 +7608,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7637,7 +7629,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7645,10 +7637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7671,13 +7663,13 @@
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7728,7 +7720,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>90</v>
@@ -7749,7 +7741,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7757,14 +7749,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7783,19 +7775,19 @@
         <v>81</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7844,7 +7836,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7862,10 +7854,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -7873,10 +7865,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7902,13 +7894,13 @@
         <v>181</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7934,11 +7926,11 @@
         <v>81</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>184</v>
+        <v>401</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
@@ -7956,7 +7948,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7974,10 +7966,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7985,10 +7977,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8011,19 +8003,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8072,7 +8064,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8090,10 +8082,10 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
